--- a/downloads/japan-1910-tables.xlsx
+++ b/downloads/japan-1910-tables.xlsx
@@ -23,6 +23,18 @@
     <sheet name="p0077_2" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="p0079_1" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="p0080_1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="p0080_2" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="p0080_3" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="p0081_1" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="p0081_2" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="p0081_3" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="p0082_1" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="p0083_1" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="p0083_2" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="p0083_3" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="p0083_4" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="p0083_5" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="p0084_1" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -915,6 +927,330 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>https://archive.org/details/japan-year-book-1910/page/n80/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>p0080_2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[Density of population by regions, end of 1904]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n80/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>p0080_3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Table (1). Distribution of Population in Rural and Urban Districts</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>13, 14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n80/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>p0081_1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Table (2). [Distribution of Population in Rural and Urban Districts (2): cities 1894 and rate per 100 population]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n81/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>p0081_2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Population by Ages and Sexes</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n81/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>p0081_3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marriages and Divorces</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n81/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>p0082_1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Married or Unmarried, by Age</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n82/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>p0083_1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Birth-Rates</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>p0083_2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Births Classified</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>p0083_3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Death-Rates</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>p0083_4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Population by Social Rank</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>p0083_5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Number of Passports Issued to Japanese Going Abroad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>p0084_1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Japanese Abroad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>17, 18</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n84/mode/1up</t>
         </is>
       </c>
     </row>
@@ -935,6 +1271,18 @@
     <hyperlink ref="A18" location="'p0077_2'!A1"/>
     <hyperlink ref="A19" location="'p0079_1'!A1"/>
     <hyperlink ref="A20" location="'p0080_1'!A1"/>
+    <hyperlink ref="A21" location="'p0080_2'!A1"/>
+    <hyperlink ref="A22" location="'p0080_3'!A1"/>
+    <hyperlink ref="A23" location="'p0081_1'!A1"/>
+    <hyperlink ref="A24" location="'p0081_2'!A1"/>
+    <hyperlink ref="A25" location="'p0081_3'!A1"/>
+    <hyperlink ref="A26" location="'p0082_1'!A1"/>
+    <hyperlink ref="A27" location="'p0083_1'!A1"/>
+    <hyperlink ref="A28" location="'p0083_2'!A1"/>
+    <hyperlink ref="A29" location="'p0083_3'!A1"/>
+    <hyperlink ref="A30" location="'p0083_4'!A1"/>
+    <hyperlink ref="A31" location="'p0083_5'!A1"/>
+    <hyperlink ref="A32" location="'p0084_1'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4387,6 +4735,1446 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>[Density of population by regions, end of 1904]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>According to the returns compiled at the end of 1904, the average density per sq. ri throughout Japan proper was 1,887. The relative rates in the different regions of the country are given below:—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n80/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Pop. per sq. ri.</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Pop. per family.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Honshu (Middle)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>2966</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>" (North)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1344</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>" (West)</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>2998</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kyushu</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>2536</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shikoku</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>5549</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Okinawa</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>3669</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hokkaido</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>164</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>No total printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shikoku 5,549 as printed (looks high, but printed so).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Table (1). Distribution of Population in Rural and Urban Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 13, 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n80/mode/1up, https://archive.org/details/japan-year-book-1910/page/n81/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Number of Villages — City</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Number of Villages — Town</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Number of Villages — Village</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Number of Villages — Total</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Towns and Cities — 1898</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Towns and Cities — 1897</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Towns and Cities — 1896</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Towns and Cities — 1895</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Under 500</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>448</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>751</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>640</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Over 500</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>3137</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>3186</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>4050</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>14575</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>14614</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>14598</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>" 2,000</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>512</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>7547</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>8059</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>8016</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>" 5,000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>417</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>925</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>1081</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>" 10,000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>186</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>153</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>138</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>" 20,000</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>" 50,000</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>" 100,000</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>" 200,000</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Over 300,000</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>" 400,000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>" 500,000</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>1114</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>12139</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>13313</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>14027</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>14782</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>14827</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>14801</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Column 'Number of Villages — City': printed total 60, parts sum to 60 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Column 'Number of Villages — Town': printed total 1,114, parts sum to 1,114 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Column 'Number of Villages — Village': printed total 12,139, parts sum to 12,139 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Column 'Number of Villages — Total': printed total 13,313, parts sum to 13,613 — does NOT reconcile (diff -300)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Column 'Towns and Cities — 1898': printed total 14,027, parts sum to 14,020 — does NOT reconcile (diff +7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Column 'Towns and Cities — 1897': printed total 14,782, parts sum to 14,782 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Column 'Towns and Cities — 1896': printed total 14,827, parts sum to 14,826 — does NOT reconcile (diff +1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Column 'Towns and Cities — 1895': printed total 14,801, parts sum to 14,815 — does NOT reconcile (diff -14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Row check City+Town+Village=Total: fails for Under 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Table continues onto p. 14 (leaf p0081): rows 'Over 300,000' to 'Total'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Header years printed '1898', '1897' (first partly damaged but legible), '1896', '1895'. The 1898 column is printed under 'Towns and Cities' though it seems to cover all villages.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Table (2). [Distribution of Population in Rural and Urban Districts (2): cities 1894 and rate per 100 population]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n81/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Cities — 1894</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1903</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1898</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1897</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1896</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1895</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1884</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Under 500</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>83.44</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>83,86</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>84.13</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>84.36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Over 500</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>14629</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>" 2,000</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>" 5,000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>" 10,000</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>133</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>" 20,000</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>" 50,000</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>" 100,000</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>" 200,000</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>" 300,000</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>" 400,000</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>" 500,000</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>14831</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A brace in the 1898 column groups the rows 'Under 500' to '" 5,000'; for 1897, 1896, 1895 and 1884 a single figure is printed against the brace for those four grades combined. It is entered in the 'Under 500' row; the cells of the other three bracketed rows are left empty (nothing printed there, not unreadable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>'83,86' (1896) printed with a comma instead of a decimal point; transcribed as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Row '" 10,000', col 'Cities — 1894': middle 3 broken but legible as '133'. Row '" 300,000', col 1884: 7 broken, read '0.76'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cities 1894: printed total 14,831, parts sum to 14,834 — does NOT reconcile (diff -3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1903: parts sum to 99.94 vs printed 100.00 — does NOT reconcile (diff +0.06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1898: parts sum to 100.00 vs printed 100.00 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1897: parts sum to 99.90 vs printed 100.00 — does NOT reconcile (diff +0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1896: parts sum to 100.00 vs printed 100.00 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1895: parts sum to 100.00 vs printed 100.00 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Rate per 100 Population — 1884: parts sum to 100.00 vs printed 100.00 — reconciles</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5068,6 +6856,4577 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Population by Ages and Sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n81/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>1903 — Male</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>1903 — Female</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>1903 — Total</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1903</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1898</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1893</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1888</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1884</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1—5</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>3041599</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>2945459</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>5987058</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5—10</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>2585272</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>2528951</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>5114223</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10—15</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>2301724</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>2246007</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>4546731</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>10,67</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>9.289999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15—20</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>2166805</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>2116058</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>4282863</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20—25</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>2128428</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>2081923</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>4210351</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>25—30</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>1965747</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>1906457</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3872204</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>8.140000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30—35</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>1541042</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>1483541</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>3024583</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>35—40</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>1520089</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>2442996</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>2963085</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>40—45</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>1186365</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>1125966</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>2312333</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>45—50</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>1279054</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>1201492</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>2480546</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>50—55</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>1133668</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>1084211</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>2217879</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>55—60</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>948112</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>925577</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>1873689</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>60—65</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>706619</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>720690</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>1427309</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>65—70</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>450735</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>499541</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>950276</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2,38</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>70—115</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>644382</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>822419</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>1466801</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>1290</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>917</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>2207</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>23600931</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>23131207</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>46732138</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Footnotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Excl. pop. in Formosa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>'10,67' (1893, age 10—15) and '2,38' (1898, age 65—70) printed with a comma for the decimal point; transcribed as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Column '1903 — Male': printed total 23,600,931, parts sum to 23,600,931 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Column '1903 — Female': printed total 23,131,207, parts sum to 24,132,205 — does NOT reconcile (diff -1,000,998)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Column '1903 — Total': printed total 46,732,138, parts sum to 46,732,138 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Male+Female=Total by row: does NOT reconcile for 10—15 (diff -1,000); 35—40 (diff -1,000,000); 40—45 (diff +2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1903: parts sum to 100.01 vs printed 100.00 — does NOT reconcile (diff -0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1898: parts sum to 99.94 vs printed 100.00 — does NOT reconcile (diff +0.06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1893: parts sum to 100.00 vs printed 100.00 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1888: parts sum to 100.00 vs printed 100.00 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Per 100 Population — 1884: parts sum to 100.00 vs printed 100.00 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Rows 10—15, 35—40, 40—45 re-read on enlarged crops: figures confirmed as printed (35—40 Female prints 2,442,996).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Marriages and Divorces</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n81/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Marriages</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Divorces</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Marriages per 1,000 pop.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Divorces per 100 pop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>378637</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>63593</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>394378</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>64311</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>371187</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>65571</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>399218</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>64016</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>351260</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>60179</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>No total printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>'Divorces per 100 pop.' heading as printed (figures look like per 1,000).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Married or Unmarried, by Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(At end of 1903)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n82/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Married — Male</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Married — Female</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Unmarried — Male</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Unmarried — Female</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Total — Male</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Total — Female</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Total — Total</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>No. of Males Per 100 Females</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1—5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>3041599</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>2954459</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>3041599</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>2954459</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>5987058</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>103.26</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5—10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>2585272</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>2528948</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>2585272</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>2528948</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>5114220</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>102.23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10—15</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>323</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>2301673</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>2244684</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>2301724</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>2245007</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>4546731</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>102.53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15—20</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>35462</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>215075</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>2131343</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1900983</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>2166805</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>2116058</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>4282863</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>102.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20—25</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>415074</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>945066</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>1713354</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1136857</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>2128428</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>2081923</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>4210351</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>102.23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>25—30</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>1013996</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>1289205</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>951751</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>617252</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>1965747</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>1906457</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>3872204</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>103.11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30—35</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>1066534</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>1117473</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>474508</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>366068</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>1541042</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>1483541</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>3024583</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>103.88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>35—40</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>1157047</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>1116154</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>363042</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>326842</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>1520089</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>1442996</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>2963085</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>105.34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>40—45</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>923278</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>853434</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>263087</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>272534</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>1186365</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>1125968</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>2312333</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>105.36</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>45—50</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>990590</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>860017</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>288464</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>341475</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>1279054</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>1201492</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>2480546</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>106.46</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>50—55</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>862696</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>706250</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>270972</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>377961</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>1133668</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1084211</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>2217879</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>104.56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>55—60</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>693591</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>513673</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>254521</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>411904</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>948112</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>925577</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>1873689</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>102.43</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>60—65</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>485928</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>317356</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>220691</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>403334</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>706619</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>720690</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>1427309</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>98.05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>65—70</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>282291</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>161373</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>168444</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" s="8" t="n">
+        <v>450735</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>499541</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>950276</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>90.28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>70—115</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1466801</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Printed rotated (landscape) on the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Row 65—70, col 'Unmarried — Female': printed '338,1?8', the fifth digit damaged (open C-shape); left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>No total row printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Row 70—115: only Total — Total (1,466,801) is printed; other cells are dashes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Row checks (married+unmarried=total by sex; male+female=total): do NOT reconcile for: 1—5 Total M+F vs Total (diff -9,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Row 1—5 re-read: female printed 2,954,459 in both Unmarried and Total columns (p. 14 table prints 2,945,459).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Birth-Rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(Exclu. Still-Births).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Females</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Births per 100 people</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Males per 100 females born</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Still-Births per 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>761980</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>725497</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1487477</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>105.03</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>9.460000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>774484</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>738606</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" s="7" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>104.86</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>9.44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>765705</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>727842</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>1493547</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="7" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>9.34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" s="8" t="n">
+        <v>704066</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" s="7" t="n">
+        <v>105.14</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>738171</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>718868</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>1457039</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>102.68</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>8.890000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Row 1902, col Total: printed '1,513,09?', last digit broken; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Row 1904, col Males: printed '74?,241', third digit damaged; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Row 1904, col Total: printed '1,44?,307', fourth digit damaged; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Row 1903, col 'Births per 100 people': printed '3.?0', first decimal damaged (looks like 2); left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Row 1904, col 'Births per 100 people': printed '3.?6', first decimal damaged (looks like 0); left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Row 1901 'Births per 100 people' printed '3 27' with a faint point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1901: Males+Females=1,487,477 vs Total 1,487,477 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1903: Males+Females=1,493,547 vs Total 1,493,547 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1905: Males+Females=1,457,039 vs Total 1,457,039 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1902: Males+Females = 1,513,090 (the damaged total's last digit not decided from this). 1904 not checkable.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Births Classified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Males per 100 Females — Legitimacy</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Males per 100 Females — Illegitimacy</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Males per 100 Females — Total</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Illegitimacy per 100 Legitimacy — Males</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Illegitimacy per 100 Legitimacy — Females</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Illegitimacy per 100 Legitimacy — Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>105.21</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>104.14</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>105.11</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>104.98</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>103.61</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>10.34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>105.48</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>102.56</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>105.21</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>10.37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>105.27</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>103.87</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>105.14</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>102.87</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Rates; no additive totals to check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1902 '10 28' and '10 41' printed with faint decimal points.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Death-Rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Females</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Deaths per 100 people</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Mortality of Males per 100 Females</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>467454</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>455072</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>922549</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>102.72</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>486418</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>472716</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>959126</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>474195</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>459633</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>933834</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>103.17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>524670</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>474946</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>999621</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>110.47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>544197</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>500682</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>1044855</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>108.69</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1901: Males+Females=922,526 vs Total 922,549 — does NOT reconcile (diff +23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1902: Males+Females=959,134 vs Total 959,126 — does NOT reconcile (diff -8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1903: Males+Females=933,828 vs Total 933,834 — does NOT reconcile (diff +6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1904: Males+Females=999,616 vs Total 999,621 — does NOT reconcile (diff +5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1905: Males+Females=1,044,879 vs Total 1,044,855 — does NOT reconcile (diff -24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>All Total cells re-read on enlarged crop; confirmed as printed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Population by Social Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(at end of 1903)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Heads of family — Sex</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Heads of family — Number</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Females</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Peers</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>784</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1786</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shizoku</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>401043</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>694092</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1034772</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Females</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>38151</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Heimin</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" s="8" t="n">
+        <v>14722688</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>21364727</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Females</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>691072</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>8172365</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>15418566</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Females</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>729223</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Grand total</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" s="8" t="n">
+        <v>23600931</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>23131207</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Footnotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>100 females per 102.03 males.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Layout: for Shizoku, Heimin and Total the heads-of-family figures are given for Males and Females separately, and a brace joins them to one Males and one Females population figure; these are entered on the first ('Males') sub-row, the second sub-row's population cells are empty (nothing printed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Grand total printed as a line: 'Grand total ...... Males 23,600,931; Females 23,131,207'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Row Heimin, Heads of family Males: printed '7,78?,538', fourth digit damaged; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Row Total, col Females: printed '22,401,98?', last digit damaged; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Swapped-looking columns: Shizoku Females (1,034,772) and Heimin Females (21,364,727) exceed Males — printed so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Males: Peers+Shizoku+Heimin = 15,418,566 vs printed Total 15,418,566 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Females: parts sum to 22,401,984; printed Total damaged (22,401,98?), not checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Heads of family Females: 38,151+691,072 = 729,223 vs Total 729,223 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Heads of family Males: Heimin damaged; not checkable. Grand totals (23,600,931 / 23,131,207) differ from the Total row (15,418,566 / 22,401,98?) — printed so.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Number of Passports Issued to Japanese Going Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n83/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Females</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>28990</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>3010</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>32900</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>31956</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>3707</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>35663</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>24981</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>2396</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>27277</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>16833</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>2396</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>19466</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>53471</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>5380</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>58851</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>36627</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>43627</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1906 Total and 1903/1907 Males printed with the thousands separator looking like a point ('58.851', '31.956', '36.627'); transcribed with commas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>No column totals printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1902: Males+Females=32,000 vs Total 32,900 — does NOT reconcile (diff +900)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1903: Males+Females=35,663 vs Total 35,663 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1904: Males+Females=27,377 vs Total 27,277 — does NOT reconcile (diff -100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1905: Males+Females=19,229 vs Total 19,466 — does NOT reconcile (diff +237)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1906: Males+Females=58,851 vs Total 58,851 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1907: Males+Females=43,627 vs Total 43,627 — reconciles</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Japanese Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 17, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(At end of 1907)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n84/mode/1up, https://archive.org/details/japan-year-book-1910/page/n85/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>19235</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="8" t="n">
+        <v>33112</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>*1,609</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>284</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Peking</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>469</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>289</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tientsin</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>1192</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>827</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Newchwang</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>1507</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>1083</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chifoo</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>217</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>191</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tsintao</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hankow</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>794</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>363</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>3912</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>6212</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fuchow</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>*285</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Amoy</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>177</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>*1,210</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>225</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kirin</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mukden</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>1398</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>1043</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Liaoyang</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>259</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>201</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Antung</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>2552</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>1915</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>4467</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Siberia</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>2580</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>2376</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>4956</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Harbin</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>292</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>325</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tsitsihar</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nicolievsk</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>198</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>253</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Vladivostock</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>1365</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>836</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Siam</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>*11</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>British Asia</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>1095</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>1838</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Hongkong</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>383</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>382</v>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>817</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Calcutta</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Amoy</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>69957</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>51986</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>121943</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>*1,620</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>284</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>320</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>243</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Austria-Hungary</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Brussel</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Holland</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>St. Petersburg</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>608</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>U. S. A.</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>18546</v>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>1534</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>20080</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>389</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>988</v>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>885</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>1345</v>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>2670</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>631</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>3301</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Tacoma</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>495</v>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>873</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>6675</v>
+      </c>
+      <c r="C66" s="8" t="n">
+        <v>1143</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>7818</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>3317</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>713</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>1968</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Klondyke</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>344</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>27189</v>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>2796</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>29985</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Argentine</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>2098</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>339</v>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>2151</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oceania (U.S.A.)</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>53934</v>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>20040</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>73974</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>52473</v>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>19609</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>72082</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>415</v>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>212</v>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Do. (British)</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>3183</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>173</v>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>3356</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Townsville</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>1216</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Do. (German)</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" s="8" t="n">
+        <v>20213</v>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>77336</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n">
+        <v>157028</v>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>75192</v>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>232220</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>* 1,620</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>284</v>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>105316</v>
+      </c>
+      <c r="C88" s="8" t="n">
+        <v>34237</v>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>139553</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>* 651</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>115530</v>
+      </c>
+      <c r="C90" s="8" t="n">
+        <v>38255</v>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>153785</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>* 909</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B92" s="8" t="n">
+        <v>117715</v>
+      </c>
+      <c r="C92" s="8" t="n">
+        <v>36921</v>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>148636</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>* 1,001</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B94" s="8" t="n">
+        <v>138185</v>
+      </c>
+      <c r="C94" s="8" t="n">
+        <v>45059</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>183244</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>* 1,132</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B96" s="8" t="n">
+        <v>198827</v>
+      </c>
+      <c r="C96" s="8" t="n">
+        <v>73419</v>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>272246</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>* 1,464</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>203</v>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Footnotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Besides there were about 1,000 in the districts in the jurisdiction of the Japanese consulate at Batavia. *=Formosans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Where a place has two lines joined by a brace (China, Fuchow, Amoy, Siam, Total), the second line (Male figure marked *) is entered as a separate row with an empty stub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Indented cities (Peking ... Antung under China; Harbin ... Vladivostock under Siberia; Hongkong, Singapore, Calcutta under British Asia; London, Paris etc. under their countries) are printed indented; indentation not recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Row China (first line), col Female: printed '12,8?7', third digit damaged; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Row Singapore, col Total: printed '1,2?0', third digit damaged; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>A second 'Amoy' (2, 7, 9) is printed after Calcutta under British Asia; transcribed as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Table continues on p. 18 (leaf p0085) from 'St. Petersburg' to the 1906 rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Row 'Total' (Oceania section, p. 18), col Male: printed '57,12?', last digit broken; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Rows 1902-1906 (comparison years) printed below the Grand Total, each with a Formosan (*) second line.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/downloads/japan-1910-tables.xlsx
+++ b/downloads/japan-1910-tables.xlsx
@@ -35,6 +35,14 @@
     <sheet name="p0083_4" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="p0083_5" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="p0084_1" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="p0085_1" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="p0086_1" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="p0086_2" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="p0086_3" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="p0091_1" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="p0091_2" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="p0092_1" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="p0092_2" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,9 +51,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -91,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +115,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1251,6 +1261,222 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>https://archive.org/details/japan-year-book-1910/page/n84/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>p0085_1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Foreigners Residing in Japan</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>18, 19</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n85/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>p0086_1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Foreigners in Japan by Districts</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n86/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>p0086_2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Foreigners in Japan by Nationality</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n86/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>p0086_3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ainu in Hokkaido</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n86/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>p0091_1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Holders of the Grand Order</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n91/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>p0091_2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Holders of the 1st Grade Golden Kite</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n91/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>p0092_1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Holders of Decorations</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n92/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>p0092_2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Holders of the Golden Kite Military Honour</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n92/mode/1up</t>
         </is>
       </c>
     </row>
@@ -1283,6 +1509,14 @@
     <hyperlink ref="A30" location="'p0083_4'!A1"/>
     <hyperlink ref="A31" location="'p0083_5'!A1"/>
     <hyperlink ref="A32" location="'p0084_1'!A1"/>
+    <hyperlink ref="A33" location="'p0085_1'!A1"/>
+    <hyperlink ref="A34" location="'p0086_1'!A1"/>
+    <hyperlink ref="A35" location="'p0086_2'!A1"/>
+    <hyperlink ref="A36" location="'p0086_3'!A1"/>
+    <hyperlink ref="A37" location="'p0091_1'!A1"/>
+    <hyperlink ref="A38" location="'p0091_2'!A1"/>
+    <hyperlink ref="A39" location="'p0092_1'!A1"/>
+    <hyperlink ref="A40" location="'p0092_2'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9849,7 +10083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11424,9 +11658,342 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Male+Female=Total by row: does NOT reconcile for Harbin (292+325=617 vs 627), Vladivostock (1,365+836=2,201 vs 2,203), 1904 (117,715+36,921=154,636 vs 148,636); re-read, confirmed as printed. All other complete rows reconcile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Indented city rows are selected places, not exhaustive sub-divisions, so country figures exceed their sums (checks below are informational).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>China (first line) = Peking…Antung non-* lines: Male 19,235 vs parts 12,764 does NOT reconcile (diff +6,471); Female: not checkable (blank cell); Total 33,112 vs parts 21,325 does NOT reconcile (diff +11,787)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>China * line = Fuchow*+Amoy*: Male *1,609 vs parts 1,495 does NOT reconcile (diff +114); Female 284 vs parts 266 does NOT reconcile (diff +18); Total 1,893 vs parts 1,761 does NOT reconcile (diff +132)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Siberia = Harbin…Vladivostock: Male 2,580 vs parts 1,884 does NOT reconcile (diff +696); Female 2,376 vs parts 1,470 does NOT reconcile (diff +906); Total 4,956 vs parts 3,366 does NOT reconcile (diff +1,590)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>British Asia = Hongkong+Singapore+Calcutta: Male 1,095 vs parts 872 does NOT reconcile (diff +223); Female 1,838 vs parts 1,302 does NOT reconcile (diff +536); Total: not checkable (blank cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Asia Total = China+Siberia+Siam+British Asia+Amoy(2nd): Male 69,957 vs parts 23,029 does NOT reconcile (diff +46,928); Female: not checkable (blank cell); Total 121,943 vs parts 41,189 does NOT reconcile (diff +80,754)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Asia Total * line = China*+Siam*: Male *1,620 vs parts 1,620 reconciles; Female 284 vs parts 284 reconciles; Total 1,904 vs parts 1,904 reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Europe Total = England…Russia (countries): Male 608 vs parts 608 reconciles; Female 86 vs parts 86 reconciles; Total 694 vs parts 694 reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>America Total = U.S.A.+Canada+Mexico: Male 27,189 vs parts 27,189 reconciles; Female 2,796 vs parts 2,796 reconciles; Total 29,985 vs parts 29,985 reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>U.S.A. = Illinois…Alaska: Male 18,546 vs parts 7,645 does NOT reconcile (diff +10,901); Female 1,534 vs parts 990 does NOT reconcile (diff +544); Total 20,080 vs parts 8,635 does NOT reconcile (diff +11,445)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>South America Total = Brazil+Argentine+Peru: Male 2,151 vs parts 2,151 reconciles; Female 111 vs parts 111 reconciles; Total 2,262 vs parts 2,262 reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Oceania Total = Oceania (U.S.A.)+Do. (British)+Do. (German): Male: not checkable (blank cell); Female 20,213 vs parts 20,213 reconciles; Total 77,336 vs parts 77,336 reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Grand Total = section Totals: Male: not checkable (blank cell); Female 75,192 vs parts 75,192 reconciles; Total 232,220 vs parts 232,220 reconciles</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Foreigners Residing in Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 18, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n85/mode/1up, https://archive.org/details/japan-year-book-1910/page/n86/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>At end of</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Females</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>10318</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>3939</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>14257</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>9903</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>3806</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>13706</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>11569</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>3928</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>15497</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>12573</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>3985</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>16558</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>14485</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>4489</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>18972</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>14561</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>4347</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>18908</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1902: Males+Females=14,257 vs Total 14,257 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1903: Males+Females=13,709 vs Total 13,706 — does NOT reconcile (diff -3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1904: Males+Females=15,497 vs Total 15,497 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1905: Males+Females=16,558 vs Total 16,558 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1906: Males+Females=18,974 vs Total 18,972 — does NOT reconcile (diff -2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1907: Males+Females=18,908 vs Total 18,908 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Rows 1906-1907 printed at top of p. 19 (leaf p0086). 1903 row re-read; confirmed as printed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11709,6 +12276,2923 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Foreigners in Japan by Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Official returns put the number of foreign residents in Japan from the end of 1904 to 1907 as follows:—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n86/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>1907 — Males</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1907 — Females</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>1907 — Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>3240</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>4232</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>5555</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>232</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>4977</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kanagawa</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>5541</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>5745</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>6088</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>4276</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>2046</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>6322</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aichi</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Miyagi</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kyoto</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>101</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Osaka</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>578</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>719</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>577</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hyogo</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>3294</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>3222</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>3727</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>2733</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>1148</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hiroshima</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Yamaguchi</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>1579</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>1534</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>1553</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1109</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>414</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fukuoka</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>243</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hokkaido</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>212</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>243</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>No total row printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1907 Males+Females=Total: all rows reconcile</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Foreigners in Japan by Nationality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nationality of foreigners numbering 100 or above is:—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n86/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>1907 — Male</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>1907 — Female</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1907 — Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>10388</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>12425</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>10239</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>2034</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>12273</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>British</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>2114</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>2155</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1442</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>851</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Americans</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>1612</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>931</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>693</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Germans</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>616</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>670</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>476</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>188</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Frenchmen</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>531</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>540</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>309</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Koreans</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>303</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>254</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Russians</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>211</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Total (inc. others)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" s="12" t="n">
+        <v>14.561</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>4347</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>18908</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total line printed as prose: 'Total (inc. others) 14.561 Males 4,347 Females 18,908 Total.' (with a point in 14.561); includes nationalities not listed, so parts are not expected to sum to it. Nothing printed for 1905/1906 in the total line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1907 Male+Female=Total: all rows reconcile</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Heading printed 'Natonality.' (sic).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Ainu in Hokkaido</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Population · printed pp. 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n86/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>At end of</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>8598</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>9034</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>19632</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>8528</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>8914</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>17442</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>8690</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>9025</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>17715</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Inc. or Dec.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>+162</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+111</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+273</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>In 1907 the birthrates and deathrates were as follows:—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>[Item]</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Birth</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" s="9" t="n">
+        <v>242</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Death</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>227</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>226</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1905: Male+Female=17,632 vs Total 19,632 — does NOT reconcile (diff +2,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1906: Male+Female=17,442 vs Total 17,442 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1907: Male+Female=17,715 vs Total 17,715 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Inc. or Dec.: Male+Female=273 vs Total +273 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Inc. or Dec. vs 1907 minus 1906: Male +162, Female +111, Total +273 — Male and Female match printed +162/+111; Total matches +273.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Part B row Birth, col Male: printed '2?0', middle digit broken; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Death: 227+226=453 — reconciles.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Holders of the Grand Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n91/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Rank and Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Yamagata</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Marshal, Prince (with Collar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Oyama</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>" " "</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Matsukata</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Marquis, Privy Councillor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Inouye</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Marquis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tokudaiji</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Marquis, Grand Chamberlain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Katsura</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Marquis, General.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Count, full-Admiral; Chief, Naval Staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Names printed in italics, each followed by a comma and leader dots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Oyama: three ditto marks under 'Marshal, Prince (with Collar)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>'Matsukata' and 'Katsura' have a broken 't'/'s' in the scan.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Holders of the 1st Grade Golden Kite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n91/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Rank and Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hasejawa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Visc., General.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Iju-in</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Baron, Vice Admiral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ito</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Count, Admiral of the Fleet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kamimura</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Baron Vice-Adm., Com. of Yokosuka Admiralty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kataoka</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Baron Admiral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kawamura</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Visc., General.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nishi</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Visc., General.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Noji</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Count, General.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Oka</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Count, General.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Oyama</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Prince, Marshal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Terauchi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Visc., Gen., Minister of War.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Count, Admiral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Yamagata</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Prince, Marshal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Yamamoto</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Count, Admiral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Names printed in italics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>'Hasejawa' as it appears in print (italic g/j; probably Hasegawa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>'Yamamoto' has a broken 't' in the scan.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Holders of Decorations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n92/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>G.O. — C.C.</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>G.O. — G.C.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>1st Class — R.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>1st Class — R.S.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1st Class — S.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>1st Class — C.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>2nd Class — R.S.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>2nd Class — S.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>2nd Class — C.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>3rd Class — R.S.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>3rd Class — S.</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>3rd Class — C.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>4th Class — R.S.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>4th Class — S.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>4th Class — C.</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>5th Class — R.S.</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>5th Class — S.</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>5th Class — C.</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>6th Class — R.S.</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>6th Class — S.</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>6th Class — C.</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>7th Class — R.S.</t>
+        </is>
+      </c>
+      <c r="X6" s="5" t="inlineStr">
+        <is>
+          <t>7th Class — S.</t>
+        </is>
+      </c>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>7th Class — C.</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
+        <is>
+          <t>8th Class — R.S.</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>8th Class — S.</t>
+        </is>
+      </c>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>8th Class — C.</t>
+        </is>
+      </c>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>163</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>1141</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>561</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>2352</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="AA7" s="9" t="n">
+        <v>758</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>808</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>1455</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA8" s="9" t="n">
+        <v>942</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC8" s="8" t="n">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>229</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>216</v>
+      </c>
+      <c r="R9" s="9" t="n">
+        <v>381</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="n">
+        <v>660</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="n">
+        <v>351</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z9" s="9" t="n">
+        <v>934</v>
+      </c>
+      <c r="AA9" s="8" t="n">
+        <v>1579</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>204</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>655</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>280</v>
+      </c>
+      <c r="R10" s="9" t="n">
+        <v>554</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>1082</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>1537</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>5278</v>
+      </c>
+      <c r="X10" s="8" t="n">
+        <v>1764</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z10" s="8" t="n">
+        <v>21692</v>
+      </c>
+      <c r="AA10" s="8" t="n">
+        <v>3144</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC10" s="8" t="n">
+        <v>36357</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>989</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>3474</v>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>107</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>13340</v>
+      </c>
+      <c r="R11" s="9" t="n">
+        <v>249</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>86782</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>3002</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>94260</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>14422</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z11" s="8" t="n">
+        <v>529388</v>
+      </c>
+      <c r="AA11" s="8" t="n">
+        <v>235268</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC11" s="8" t="n">
+        <v>981461</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>910</v>
+      </c>
+      <c r="O12" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>1123</v>
+      </c>
+      <c r="R12" s="9" t="n">
+        <v>480</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>1838</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>2478</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>3650</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>2881</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>212</v>
+      </c>
+      <c r="Z12" s="8" t="n">
+        <v>10244</v>
+      </c>
+      <c r="AA12" s="8" t="n">
+        <v>11522</v>
+      </c>
+      <c r="AB12" s="8" t="n">
+        <v>1742</v>
+      </c>
+      <c r="AC12" s="8" t="n">
+        <v>37602</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Footnotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Notes:—G.O. Grand Order. C.C. Crysan'mum Collar. G.C. Grand Corden Cry'mum. R. Rising Sun and Paulonia. R.S Rising Sun. S. Sacred Treasury. C. Crown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Printed rotated (landscape) on the page. Print is very small and bold; 3/8 and 5/6 are hard to tell apart in this scan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Blank (ambiguous glyphs): 1903 'G.O. — G.C.' and '1st Class — R.' (each 3 or 8); 1906 '1st Class — R.S.' (printed '?0', first digit 3 or 8); 1902 '7th Class — C.' (5 or 6); 1902 Total (first digit 5 or 6: '?,391'); 1904 '6th Class — S.' ('?56', first digit 5 or 6); 1904 '7th Class — S.' ('?88', first digit 5 or 6); 1904 Total ('?,862', first digit 5 or 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1902: row total not checkable (blank cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1903: row total not checkable (blank cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1904: row total not checkable (blank cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1905: printed Total 36,357, parts sum to 36,353 — does NOT reconcile (diff +4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1906: row total not checkable (blank cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1907: printed Total 37,602, parts sum to 37,592 — does NOT reconcile (diff +10)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Holders of the Golden Kite Military Honour</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n92/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>1st Merit</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>189[illegible]</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>814</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" s="8" t="n">
+        <v>1285</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" s="8" t="n">
+        <v>26497</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>27649</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>380</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1632</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>1837</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>3358</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>66533</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>73810</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1037</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>437</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="8" t="n">
+        <v>3569</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>3728</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>95443</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>105128</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Footnotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>The annuities given in 1907 totalled yen 9,063,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Printed rotated (landscape) on the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Row 1 year label printed '189?', last digit broken; marked [illegible].</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Row 1904, col 6th: printed '?9', first digit damaged; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total row, col 4th: printed '1,85?', last digit damaged; left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>189[illegible]: Total 5, parts 5 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1901: Total 188, parts 188 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1904: row not checkable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1906: Total 73,810, parts 73,810 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1907: Total 1,160, parts 1,160 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Column 1st Merit: Total 17, parts 17 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Column 2nd: Total 76, parts 76 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Column 3rd: Total 437, parts 437 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Column 4th: not checkable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Column 5th: Total 3,569, parts 3,569 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Column 6th: not checkable</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Column 7th: Total 95,443, parts 95,443 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Column Total: Total 105,128, parts 105,128 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Row 1905, col 6th: printed '2?2', middle digit faint/broken; left blank. 1905 row therefore not checkable.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/downloads/japan-1910-tables.xlsx
+++ b/downloads/japan-1910-tables.xlsx
@@ -43,6 +43,12 @@
     <sheet name="p0091_2" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="p0092_1" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="p0092_2" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="p0093_1" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="p0093_2" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="p0094_1" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="p0094_2" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="p0094_3" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="p0095_1" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1477,6 +1483,168 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>https://archive.org/details/japan-year-book-1910/page/n92/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>p0093_1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[Number of Peers] (The Peerage and Ranks)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n93/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>p0093_2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>List of Princes</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n93/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>p0094_1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>List of Marquises</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n94/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>p0094_2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Precedent at Court According to Rank</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n94/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>p0094_3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Principal Officials of the Imperial Household Dept.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>27, 28</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n94/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>p0095_1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Imperial Court</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Court Ladies</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/japan-year-book-1910/page/n95/mode/1up</t>
         </is>
       </c>
     </row>
@@ -1517,6 +1685,12 @@
     <hyperlink ref="A38" location="'p0091_2'!A1"/>
     <hyperlink ref="A39" location="'p0092_1'!A1"/>
     <hyperlink ref="A40" location="'p0092_2'!A1"/>
+    <hyperlink ref="A41" location="'p0093_1'!A1"/>
+    <hyperlink ref="A42" location="'p0093_2'!A1"/>
+    <hyperlink ref="A43" location="'p0094_1'!A1"/>
+    <hyperlink ref="A44" location="'p0094_2'!A1"/>
+    <hyperlink ref="A45" location="'p0094_3'!A1"/>
+    <hyperlink ref="A46" location="'p0095_1'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15198,6 +15372,897 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>[Number of Peers] (The Peerage and Ranks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The number of Peers and its movement are shown in the following list:—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n93/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Prince</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Marquis</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Viscount</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Baron</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>362</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>290</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>362</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>290</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>363</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>289</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>362</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>291</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>363</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>304</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>375</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>376</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1902: Total 789, parts 789 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1903: Total 789, parts 789 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1904: Total 789, parts 789 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1905: Total 790, parts 790 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1906: Total 804, parts 803 — does NOT reconcile (diff +1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1907: Total 902, parts 902 — reconciles</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Headings printed 'Connt.' and 'Visconnt.' (broken u).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>List of Princes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(For life see Chap. Who's Who).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n93/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ichijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ito</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Iwakura</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Konoye</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kujo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mōri</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Nijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Oyama</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sanjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Shimazu (main house)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>" (scion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Takatsukasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tokugawa (main house)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tokugawa (last of Shoguns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Yamagata</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Printed in two columns; left column (Ichijo … Oyama) then right column (Sanjo … Yamagata).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>'" (scion)' = ditto mark under Shimazu.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>List of Marquises</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(For life see Chap. Who's Who)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n94/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Asano</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Daigo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hachisuka</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hirohata</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hosokawa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ikeda (Bizen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ikeda (Inaba)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Inouye</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Katsura</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kazan-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kido</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kikutei</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kuga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kuroda</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mayeda</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Matsudaira</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Matsukata</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Nabeshima</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nakamikado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nakayama</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Nozu</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Okubo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Oimikado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Saga</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Saigo (son of elder Saigo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Saigo (son of junior Saigo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Saionji</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sasaki (cr. '09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Satake</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Shijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sho</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tokudaiji</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Tokugawa (house of Kishu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>" ( " " Mito)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>" ( " " Owari)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Yamanouchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Printed in two columns; left column (Asano … Nabeshima) then right column (Nakamikado … Yamanouchi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ditto rows under 'Tokugawa (house of Kishu)' printed as '" ( " " Mito)' and '" ( " " Owari)'.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -15542,6 +16607,1177 @@
       <c r="A36" t="inlineStr">
         <is>
           <t>Rows 1-18 on p. 1, rows 19-23 on p. 2. No total printed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Precedent at Court According to Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n94/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Rank (in order of precedence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Holders of the Grand Order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Prime Minister.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ministers of State.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>President of the Privy Council.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Marshals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Admirals of the Fleet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Full Generals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Full Admirals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Grand Chamberlain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vice-President of the Privy Council.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Privy Councillors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Holders of 1st class Order of the Rising Sun and Paulownia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Princes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Holders of 1st class Order of the Rising Sun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Holders of 1st class Order of the Sacred Treasure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Grand Master of Ceremonies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Grand Master of Ritualist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Lord Steward to the Empress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>President of the Administrative Litigation Court.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Civil and Military Officers of 1st grade Higher Service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Marquises.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Civil and Military Officers of 2nd grade Higher Service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lords in Walting of Jukō Hall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lords in Waiting of Kinkei Hall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Holders of 2nd class Order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Viscounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Holders of 3rd class Order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Barons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Printed in two columns, read left column then right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>'Precedent' (title), 'Walting' and 'Ritualist' as printed. Jukō and Kinkei printed in italics.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Principal Officials of the Imperial Household Dept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n94/mode/1up, https://archive.org/details/japan-year-book-1910/page/n95/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Holder(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Minister</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Prince T. Iwakura</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vice-Minister</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Visc. Watanabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Imperial Treasury</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>J. Yoshida, S. Sakamoto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Imperial Archives</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E. Yamaguchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Imperial Cookery</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Count K. Kagawa</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Police Affairs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T. Ogasawara</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dr. T. Katayama</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gardening</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vis. Fukuha</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Imperial Mews.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vis. Fujinami</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Imperial Forest Bureau</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C. Wa[illegible]abe Visc. Y. Sasaki</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Peerage Bureau</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Marquis. M. Kuga, S. Obara</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Medical Affairs</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Baron. Dr. Oka; Baron T. Komeda</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Supplies and Purchase</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S. Nagasaki</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Privy Seals</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Marq. Tokudaiji, T. Matano</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Board of Ceremonies</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Holder(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Grand Master of Ceremonies</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Count U. Toda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Vice-Grand Master</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H. Ito</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Members</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S. Nagasaki; Marquis. Kido; R. Niwa; K. Yamanouchi; Vis. Fukuha; Y. Yoshida; M. Ichiki; Vis. [illegible]aba; Count Mayeda</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Court Councillors</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Baron S. Osaki, C. Nabeshima, M. Funakoshi, Baron M. Katori, Major-Gen. M. Sato, Vis. Takatsuji, Baron Dr. Ikeda, Vis. Fujinami, S. Nagasaki, Baron. Y. Sonoda, Marq. T. Nakayama, Prince Nijo, Marquis Kido, Prof. Y. Hozumi, Prof. K. Okano, Y. Okuda, S. Hirayama, Vis. Higashisono, Vis. Hojo, K. Maruo. Major-Gen. S. Tauchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Board of Chamberlains</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Holder(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Grand Chamberlain</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Marquis. S. Tokudaiji</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Vice-Grand Chamberlain</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Prince T. Iwakura</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chamberlains</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Baron T. Komeda; Viscount M. Higashizono; Viscount U. Hōjō; Y. Hineno; S. Hinonishi; K. [illegible]; S. Shimizutani</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Aide-de-Camp. to H. I.M.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>General Baron Nakamura; Rear-Adm. Baron Nishi</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>The Empress' Household</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Holder(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Viscount Kagawa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>The Crown Prince's Household</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Holder(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Lieut.-General Baron Muraki</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Grand Chamberlain</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Prince S. Ichijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chief Aide-de-Camp to the Crown [Prince]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Lieut.-General Baron Muraki</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Printed as run-on text ('Office, Name; Office, Name; …'), split here into Office / Holder(s); names are in italics. Continues from p. 27 onto p. 28 with sub-headings Board of Ceremonies, Board of Chamberlains, The Empress' Household, The Crown Prince's Household.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Italic w often looks like 'u' in the scan: printed forms appear as 'Kagaua', 'Ogasauara', 'Iuakura' (twice), 'Kagaua' (Empress' Household); transcribed Kagawa, Ogasawara, Iwakura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>'Ka'ayama' (broken t) transcribed Katayama; 'Sakamoto' has a broken t.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Imperial Forest Bureau: 'C. Wa?a?abe' — letters broken, marked [illegible]; no punctuation visible between 'C. Wa…abe' and 'Visc. Y. Sasaki'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Medical Affairs: printed 'Baron. Dr. Oka;' at foot of p. 27, then 'Baron T. Komeda;' at top of p. 28 before 'Supplies and Purchase'; both kept under Medical Affairs as the layout gives no other office.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Board of Ceremonies Members: 'Vis. ?aba' first letter(s) broken, marked [illegible]. Board of Chamberlains: 'K. ??ewahire' unreadable, marked [illegible].</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Crown Prince's Household: 'Princ S. Ichijo' and 'Chief Aide-de-Camp to the Crown Lieut.-General Baron Muraki' printed so (line ends with a stray 'e'); '[Prince]' supplied in the office label.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Contents'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Court Ladies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Imperial Court · printed pp. 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ladies on service at the Court and their official rank are as follows:—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scan: https://archive.org/details/japan-year-book-1910/page/n95/mode/1up</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>← Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>"Tenji,"</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Takakura Toshi-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yanagiwara Ai-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>"Gon Tenji,"</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chikusa To-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>" "</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ogura Fumi-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>" "</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sone Yasu-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>" "</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anekoji Yoshi-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>" " (acting)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nishi-itsutsuji Sho-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>"Shoji"</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mibu Hiro-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Koike Michi-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>" (acting)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nakayama Ei-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kinoshita Han-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>"Gon Shoji"</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Yobu Kine-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>" "</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kitajima Ito-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>" "</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tsumori Yoshi-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>" "</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Awadaguchi Ayu-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>" " (acting)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kagawa Shic-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>" "</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hirotori Kun-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Footnotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Besides the above there are eight ladies of "Myobu" rank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Transcriber's notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Rank names printed in quotation marks; ditto marks (") repeat the rank above and are kept as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Names in italics. 'Yanagiwara' and 'Kagawa' printed with an italic w that looks like 'u' ('Yanagiuara', 'Kagaua').</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>'Yobu Kine-ko', 'Shic-ko' and 'Hirotori' as they appear in the scan (letters partly broken: 'Yc bu', 'Hiro'ori').</t>
         </is>
       </c>
     </row>
